--- a/HARGA ONLINE.xlsx
+++ b/HARGA ONLINE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37844CA3-C4AE-4042-98E0-ACF6631352C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68826ABA-4A65-42D6-AE3A-B9501028387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10245" yWindow="0" windowWidth="10245" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="105">
   <si>
     <t>No.</t>
   </si>
@@ -337,6 +337,9 @@
   </si>
   <si>
     <t>HIJAB BERGO JERSEY BY DAMA</t>
+  </si>
+  <si>
+    <t>Paket Wakaf Hemat Isi 50 Alquran Al Aqeel Murah Kertas Koran / HVS | Semarang</t>
   </si>
 </sst>
 </file>
@@ -439,7 +442,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -484,6 +487,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -765,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.140625" bestFit="1" customWidth="1"/>
@@ -1882,8 +1888,8 @@
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
-        <v>62</v>
+      <c r="B67" s="18" t="s">
+        <v>104</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>6</v>
@@ -1896,8 +1902,8 @@
       </c>
     </row>
     <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
-        <v>62</v>
+      <c r="B68" s="18" t="s">
+        <v>104</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>63</v>
@@ -1910,8 +1916,8 @@
       </c>
     </row>
     <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" t="s">
-        <v>62</v>
+      <c r="B69" s="18" t="s">
+        <v>104</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>64</v>
@@ -1925,44 +1931,44 @@
     </row>
     <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E70" s="10">
-        <v>8500</v>
+        <v>725000</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E71" s="10">
-        <v>21000</v>
+        <v>625000</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E72" s="10">
-        <v>12500</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -1970,162 +1976,159 @@
         <v>65</v>
       </c>
       <c r="C73" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" s="10">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E74" s="10">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>65</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="10">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>65</v>
+      </c>
+      <c r="C76" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D76" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E73" s="10">
+      <c r="E76" s="10">
         <v>14500</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B74" t="s">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
         <v>67</v>
       </c>
-      <c r="E74" s="10">
+      <c r="E77" s="10">
         <v>14500</v>
       </c>
     </row>
-    <row r="75" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="14"/>
-      <c r="B75" t="s">
+    <row r="78" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="14"/>
+      <c r="B78" t="s">
         <v>83</v>
       </c>
-      <c r="C75" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D75" s="14" t="s">
+      <c r="C78" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E75" s="14">
+      <c r="E78" s="14">
         <v>12500</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="13"/>
-      <c r="B76" t="s">
-        <v>83</v>
-      </c>
-      <c r="C76" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E76" s="13">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="13"/>
-      <c r="B77" t="s">
-        <v>84</v>
-      </c>
-      <c r="C77" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E77" s="13">
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="13"/>
-      <c r="B78" t="s">
-        <v>85</v>
-      </c>
-      <c r="C78" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E78" s="13">
-        <v>75000</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="13"/>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E79" s="13">
-        <v>72000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="13"/>
       <c r="B80" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E80" s="13">
-        <v>50000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="13"/>
       <c r="B81" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>69</v>
       </c>
       <c r="E81" s="13">
-        <v>26000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="13"/>
       <c r="B82" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>69</v>
       </c>
       <c r="E82" s="13">
-        <v>21000</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="13"/>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C83" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E83" s="13">
-        <v>18500</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="13"/>
       <c r="B84" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C84" s="13" t="s">
         <v>10</v>
@@ -2134,43 +2137,43 @@
         <v>69</v>
       </c>
       <c r="E84" s="13">
-        <v>24000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="13"/>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C85" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E85" s="13">
-        <v>39000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="13"/>
       <c r="B86" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E86" s="13">
-        <v>9000</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="13"/>
       <c r="B87" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C87" s="13" t="s">
         <v>10</v>
@@ -2179,52 +2182,52 @@
         <v>69</v>
       </c>
       <c r="E87" s="13">
-        <v>7200</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="13"/>
       <c r="B88" t="s">
-        <v>92</v>
-      </c>
-      <c r="C88" t="s">
-        <v>16</v>
-      </c>
-      <c r="D88" t="s">
-        <v>80</v>
-      </c>
-      <c r="E88" s="16">
-        <v>26000</v>
+        <v>89</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E88" s="13">
+        <v>39000</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="13"/>
       <c r="B89" t="s">
-        <v>92</v>
-      </c>
-      <c r="C89" t="s">
-        <v>20</v>
-      </c>
-      <c r="D89" t="s">
-        <v>80</v>
-      </c>
-      <c r="E89" s="16">
-        <v>24000</v>
+        <v>90</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89" s="13">
+        <v>9000</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="13"/>
       <c r="B90" t="s">
-        <v>92</v>
-      </c>
-      <c r="C90" t="s">
-        <v>79</v>
-      </c>
-      <c r="D90" t="s">
-        <v>80</v>
-      </c>
-      <c r="E90" s="16">
-        <v>18000</v>
+        <v>91</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90" s="13">
+        <v>7200</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2233,13 +2236,13 @@
         <v>92</v>
       </c>
       <c r="C91" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="D91" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E91" s="16">
-        <v>14500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2248,70 +2251,70 @@
         <v>92</v>
       </c>
       <c r="C92" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D92" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E92" s="16">
-        <v>12500</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="13"/>
       <c r="B93" t="s">
-        <v>93</v>
-      </c>
-      <c r="C93" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D93" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E93" s="13">
-        <v>14500</v>
+        <v>92</v>
+      </c>
+      <c r="C93" t="s">
+        <v>79</v>
+      </c>
+      <c r="D93" t="s">
+        <v>80</v>
+      </c>
+      <c r="E93" s="16">
+        <v>18000</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="13"/>
       <c r="B94" t="s">
-        <v>94</v>
-      </c>
-      <c r="C94" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E94" s="13">
-        <v>18000</v>
+        <v>92</v>
+      </c>
+      <c r="C94" t="s">
+        <v>79</v>
+      </c>
+      <c r="D94" t="s">
+        <v>81</v>
+      </c>
+      <c r="E94" s="16">
+        <v>14500</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="13"/>
       <c r="B95" t="s">
-        <v>94</v>
-      </c>
-      <c r="C95" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D95" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E95" s="13">
-        <v>27000</v>
+        <v>92</v>
+      </c>
+      <c r="C95" t="s">
+        <v>79</v>
+      </c>
+      <c r="D95" t="s">
+        <v>82</v>
+      </c>
+      <c r="E95" s="16">
+        <v>12500</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="13"/>
       <c r="B96" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E96" s="13">
         <v>14500</v>
@@ -2320,133 +2323,178 @@
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="13"/>
       <c r="B97" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D97" s="13" t="s">
         <v>69</v>
       </c>
       <c r="E97" s="13">
-        <v>14500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="13"/>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E98" s="13">
-        <v>18000</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="13"/>
       <c r="B99" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="E99" s="13">
-        <v>14325</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="13"/>
       <c r="B100" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="E100" s="13">
-        <v>8100</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="13"/>
       <c r="B101" t="s">
-        <v>100</v>
-      </c>
-      <c r="C101" s="13"/>
+        <v>97</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>72</v>
+      </c>
       <c r="D101" s="13" t="s">
         <v>71</v>
       </c>
       <c r="E101" s="13">
-        <v>8500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="13"/>
       <c r="B102" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C102" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D102" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D102" s="13" t="s">
-        <v>69</v>
-      </c>
       <c r="E102" s="13">
-        <v>12500</v>
+        <v>14325</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="13"/>
       <c r="B103" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D103" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E103" s="17">
-        <v>25577</v>
+      <c r="E103" s="13">
+        <v>8100</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="13"/>
       <c r="B104" t="s">
-        <v>102</v>
-      </c>
-      <c r="C104" s="13" t="s">
-        <v>75</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C104" s="13"/>
       <c r="D104" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E104" s="17">
-        <v>25577</v>
+        <v>71</v>
+      </c>
+      <c r="E104" s="13">
+        <v>8500</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="13"/>
       <c r="B105" t="s">
+        <v>100</v>
+      </c>
+      <c r="C105" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="13">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="13"/>
+      <c r="B106" t="s">
+        <v>101</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D106" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E106" s="17">
+        <v>25577</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="13"/>
+      <c r="B107" t="s">
+        <v>102</v>
+      </c>
+      <c r="C107" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E107" s="17">
+        <v>25577</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="13"/>
+      <c r="B108" t="s">
         <v>103</v>
       </c>
-      <c r="C105" s="13" t="s">
+      <c r="C108" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D105" s="13" t="s">
+      <c r="D108" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E105" s="17">
+      <c r="E108" s="17">
         <v>25577</v>
       </c>
     </row>

--- a/HARGA ONLINE.xlsx
+++ b/HARGA ONLINE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68826ABA-4A65-42D6-AE3A-B9501028387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FF5B66-2487-4CB0-9863-B6DBBDBE284B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1860" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="2040" windowWidth="15375" windowHeight="8085" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="106">
   <si>
     <t>No.</t>
   </si>
@@ -340,6 +340,9 @@
   </si>
   <si>
     <t>Paket Wakaf Hemat Isi 50 Alquran Al Aqeel Murah Kertas Koran / HVS | Semarang</t>
+  </si>
+  <si>
+    <t>Alquran Edisi Tahlilan Al Aqeel A6 Kertas HVS 18 Baris | GARUT | Alquran Untuk Wakaf Hadiah Souvenir Hampers</t>
   </si>
 </sst>
 </file>
@@ -442,7 +445,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -487,8 +490,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -771,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.140625" bestFit="1" customWidth="1"/>
@@ -2498,6 +2504,20 @@
         <v>25577</v>
       </c>
     </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
+        <v>105</v>
+      </c>
+      <c r="C109" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E109" s="13">
+        <v>14500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/HARGA ONLINE.xlsx
+++ b/HARGA ONLINE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FF5B66-2487-4CB0-9863-B6DBBDBE284B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DEA2A3-86A0-4433-92A2-17FD46212978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2040" windowWidth="15375" windowHeight="8085" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3150" yWindow="2835" windowWidth="15375" windowHeight="8085" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="107">
   <si>
     <t>No.</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>Alquran Edisi Tahlilan Al Aqeel A6 Kertas HVS 18 Baris | GARUT | Alquran Untuk Wakaf Hadiah Souvenir Hampers</t>
+  </si>
+  <si>
+    <t>Al-Qur'an Edisi Tahlilan A6 | Custom Pengganti Yasin | 30 Juz Dengan Yasin Tahlil Terjemah | Semarang</t>
   </si>
 </sst>
 </file>
@@ -445,7 +448,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -496,6 +499,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -777,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.140625" bestFit="1" customWidth="1"/>
@@ -2511,10 +2515,21 @@
       <c r="C109" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D109" s="19" t="s">
+      <c r="D109" s="13" t="s">
         <v>68</v>
       </c>
       <c r="E109" s="13">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
+        <v>106</v>
+      </c>
+      <c r="D110" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E110" s="20">
         <v>14500</v>
       </c>
     </row>

--- a/HARGA ONLINE.xlsx
+++ b/HARGA ONLINE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DEA2A3-86A0-4433-92A2-17FD46212978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCEE9239-74A8-4F2A-A8B4-56FFE9A1826D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="2835" windowWidth="15375" windowHeight="8085" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="112">
   <si>
     <t>No.</t>
   </si>
@@ -346,6 +346,21 @@
   </si>
   <si>
     <t>Al-Qur'an Edisi Tahlilan A6 | Custom Pengganti Yasin | 30 Juz Dengan Yasin Tahlil Terjemah | Semarang</t>
+  </si>
+  <si>
+    <t>Alquran Edisi Tahlilan A6 Pengganti Buku Yasin Terjemah | MEDAN</t>
+  </si>
+  <si>
+    <t>Alquran Edisi Tahlilan A6 HVS | Custom Pengganti Yasin | 30 Juz Dengan Yasin Tahlil Terjemah | Yogyakarta</t>
+  </si>
+  <si>
+    <t>AL-AQEEL PASTEL A5</t>
+  </si>
+  <si>
+    <t>A5 (10,5X14,5CM)</t>
+  </si>
+  <si>
+    <t>A3</t>
   </si>
 </sst>
 </file>
@@ -448,7 +463,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -495,9 +510,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -781,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.140625" bestFit="1" customWidth="1"/>
@@ -904,7 +916,7 @@
     </row>
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <f t="shared" ref="A8:A63" si="0">A7+1</f>
+        <f t="shared" ref="A8:A76" si="0">A7+1</f>
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1141,26 +1153,26 @@
     </row>
     <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>A21+1</f>
+        <v>1</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E23" s="5">
-        <v>21000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>A21+1</f>
+        <v>1</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>39</v>
@@ -1169,16 +1181,16 @@
         <v>10</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="E24" s="5">
-        <v>31000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>A22+1</f>
+        <v>7</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>39</v>
@@ -1187,16 +1199,16 @@
         <v>10</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="E25" s="5">
-        <v>14000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>A22+1</f>
+        <v>7</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>39</v>
@@ -1205,61 +1217,70 @@
         <v>10</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="5">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="5">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="5">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E29" s="5">
         <v>8500</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="5">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="5">
-        <v>63000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-      <c r="B29" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="5">
-        <v>105000</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>10</v>
@@ -1268,58 +1289,58 @@
         <v>8</v>
       </c>
       <c r="E30" s="5">
-        <v>147000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E31" s="5">
-        <v>8500</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E32" s="5">
-        <v>25500</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E33" s="5">
-        <v>42500</v>
+        <v>147000</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>10</v>
@@ -1328,67 +1349,58 @@
         <v>14</v>
       </c>
       <c r="E34" s="5">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="5">
+        <v>25500</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="3"/>
+      <c r="B36" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="5">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="3"/>
+      <c r="B37" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="5">
         <v>59500</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
-        <f>A26+1</f>
-        <v>11</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E35" s="5">
-        <v>31000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="5">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="5">
-        <v>14000</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <f t="shared" si="0"/>
-        <v>14</v>
+        <f>A28+1</f>
+        <v>10</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>40</v>
@@ -1397,55 +1409,55 @@
         <v>10</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="E38" s="5">
-        <v>8500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <f>A29+1</f>
+        <v>11</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="E39" s="5">
-        <v>14000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f>A29+1</f>
+        <v>11</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E40" s="5">
-        <v>14000</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>10</v>
@@ -1454,106 +1466,106 @@
         <v>8</v>
       </c>
       <c r="E41" s="5">
-        <v>26000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E42" s="5">
-        <v>33000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E43" s="5">
-        <v>50000</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E44" s="5">
-        <v>68000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E45" s="5">
-        <v>26000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="5">
-        <v>75000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>15</v>
@@ -1562,88 +1574,88 @@
         <v>8</v>
       </c>
       <c r="E47" s="5">
-        <v>72000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E48" s="5">
-        <v>17000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E49" s="5">
-        <v>18000</v>
+        <v>68000</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E50" s="5">
-        <v>39000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E51" s="5">
-        <v>24000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>15</v>
@@ -1652,688 +1664,727 @@
         <v>8</v>
       </c>
       <c r="E52" s="5">
-        <v>32000</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E53" s="5">
-        <v>19000</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E54" s="5">
-        <v>7200</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E55" s="5">
-        <v>9000</v>
+        <v>43000</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E56" s="5">
-        <v>25200</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E57" s="5">
-        <v>25200</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>28</v>
+        <f t="shared" ref="A58:A60" si="1">A52+1</f>
+        <v>24</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E58" s="5">
-        <v>12000</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>30</v>
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E59" s="5">
-        <v>21000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E60" s="7">
-        <v>64800</v>
+        <v>17</v>
+      </c>
+      <c r="E60" s="5">
+        <v>43000</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C61" s="8" t="s">
+        <f>A55+1</f>
+        <v>27</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E61" s="7">
-        <v>48600</v>
+        <v>8</v>
+      </c>
+      <c r="E61" s="5">
+        <v>24000</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>10</v>
+        <v>28</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E62" s="7">
-        <v>48600</v>
+        <v>8</v>
+      </c>
+      <c r="E62" s="5">
+        <v>32000</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E63" s="10">
-        <v>4750</v>
+        <f t="shared" ref="A63:A65" si="2">A59+1</f>
+        <v>26</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="5">
+        <v>19000</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="12"/>
-      <c r="B64" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>6</v>
+      <c r="A64" s="3">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E64" s="10">
-        <v>725000</v>
+        <v>14</v>
+      </c>
+      <c r="E64" s="5">
+        <v>19000</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="12"/>
-      <c r="B65" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>63</v>
+      <c r="A65" s="3">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="10">
-        <v>625000</v>
+        <v>14</v>
+      </c>
+      <c r="E65" s="5">
+        <v>19000</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B66" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C66" s="12" t="s">
-        <v>64</v>
+      <c r="A66" s="3">
+        <f>A62+1</f>
+        <v>29</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="10">
-        <v>400000</v>
+      <c r="E66" s="5">
+        <v>19000</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B67" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>6</v>
+      <c r="A67" s="3">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E67" s="10">
+      <c r="E67" s="5">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="5">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" s="5">
+        <v>25200</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" s="5">
+        <v>25200</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" s="5">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E72" s="5">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73" s="7">
+        <v>64800</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" s="7">
+        <v>48600</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E75" s="7">
+        <v>48600</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E76" s="10">
+        <v>4750</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="12"/>
+      <c r="B77" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E77" s="10">
         <v>725000</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="18" t="s">
+    <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A78" s="12"/>
+      <c r="B78" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="10">
+        <v>625000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B79" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" s="10">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B80" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C80" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E80" s="10">
+        <v>725000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B81" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C81" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D81" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E68" s="10">
+      <c r="E81" s="10">
         <v>625000</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="18" t="s">
+    <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B82" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C69" s="12" t="s">
+      <c r="C82" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D82" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E69" s="10">
+      <c r="E82" s="10">
         <v>400000</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B70" t="s">
+    <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
         <v>62</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C83" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E70" s="10">
+      <c r="E83" s="10">
         <v>725000</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B71" t="s">
+    <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
         <v>62</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C84" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D84" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E71" s="10">
+      <c r="E84" s="10">
         <v>625000</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B72" t="s">
+    <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
         <v>62</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C85" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D85" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E72" s="10">
+      <c r="E85" s="10">
         <v>400000</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B73" t="s">
+    <row r="86" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
         <v>65</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C86" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D86" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E73" s="10">
+      <c r="E86" s="10">
         <v>8500</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B74" t="s">
+    <row r="87" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
         <v>65</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C87" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D87" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E74" s="10">
+      <c r="E87" s="10">
         <v>21000</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B75" t="s">
+    <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
         <v>65</v>
       </c>
-      <c r="C75" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D75" s="3" t="s">
+      <c r="C88" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E75" s="10">
+      <c r="E88" s="10">
         <v>12500</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
+    <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
         <v>65</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C89" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E76" s="10">
+      <c r="E89" s="10">
         <v>14500</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B77" t="s">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
         <v>67</v>
       </c>
-      <c r="E77" s="10">
+      <c r="E90" s="10">
         <v>14500</v>
       </c>
     </row>
-    <row r="78" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="14"/>
-      <c r="B78" t="s">
+    <row r="91" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="14"/>
+      <c r="B91" t="s">
         <v>83</v>
       </c>
-      <c r="C78" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D78" s="14" t="s">
+      <c r="C91" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E78" s="14">
+      <c r="E91" s="14">
         <v>12500</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="13"/>
-      <c r="B79" t="s">
-        <v>83</v>
-      </c>
-      <c r="C79" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E79" s="13">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="13"/>
-      <c r="B80" t="s">
-        <v>84</v>
-      </c>
-      <c r="C80" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E80" s="13">
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="13"/>
-      <c r="B81" t="s">
-        <v>85</v>
-      </c>
-      <c r="C81" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D81" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E81" s="13">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="13"/>
-      <c r="B82" t="s">
-        <v>86</v>
-      </c>
-      <c r="C82" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D82" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E82" s="13">
-        <v>72000</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="13"/>
-      <c r="B83" t="s">
-        <v>87</v>
-      </c>
-      <c r="C83" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D83" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="E83" s="13">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="13"/>
-      <c r="B84" t="s">
-        <v>87</v>
-      </c>
-      <c r="C84" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D84" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E84" s="13">
-        <v>26000</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="13"/>
-      <c r="B85" t="s">
-        <v>88</v>
-      </c>
-      <c r="C85" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D85" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E85" s="13">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="13"/>
-      <c r="B86" t="s">
-        <v>88</v>
-      </c>
-      <c r="C86" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D86" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E86" s="13">
-        <v>18500</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="13"/>
-      <c r="B87" t="s">
-        <v>89</v>
-      </c>
-      <c r="C87" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D87" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E87" s="13">
-        <v>24000</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="13"/>
-      <c r="B88" t="s">
-        <v>89</v>
-      </c>
-      <c r="C88" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D88" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="E88" s="13">
-        <v>39000</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="13"/>
-      <c r="B89" t="s">
-        <v>90</v>
-      </c>
-      <c r="C89" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D89" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E89" s="13">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="13"/>
-      <c r="B90" t="s">
-        <v>91</v>
-      </c>
-      <c r="C90" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D90" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E90" s="13">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="13"/>
-      <c r="B91" t="s">
-        <v>92</v>
-      </c>
-      <c r="C91" t="s">
-        <v>16</v>
-      </c>
-      <c r="D91" t="s">
-        <v>80</v>
-      </c>
-      <c r="E91" s="16">
-        <v>26000</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="13"/>
       <c r="B92" t="s">
-        <v>92</v>
-      </c>
-      <c r="C92" t="s">
-        <v>20</v>
-      </c>
-      <c r="D92" t="s">
-        <v>80</v>
-      </c>
-      <c r="E92" s="16">
-        <v>24000</v>
+        <v>83</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E92" s="13">
+        <v>28000</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="13"/>
       <c r="B93" t="s">
-        <v>92</v>
-      </c>
-      <c r="C93" t="s">
-        <v>79</v>
-      </c>
-      <c r="D93" t="s">
-        <v>80</v>
-      </c>
-      <c r="E93" s="16">
-        <v>18000</v>
+        <v>84</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E93" s="13">
+        <v>14000</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="13"/>
       <c r="B94" t="s">
-        <v>92</v>
-      </c>
-      <c r="C94" t="s">
-        <v>79</v>
-      </c>
-      <c r="D94" t="s">
-        <v>81</v>
-      </c>
-      <c r="E94" s="16">
-        <v>14500</v>
+        <v>85</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="13">
+        <v>75000</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="13"/>
       <c r="B95" t="s">
-        <v>92</v>
-      </c>
-      <c r="C95" t="s">
-        <v>79</v>
-      </c>
-      <c r="D95" t="s">
-        <v>82</v>
-      </c>
-      <c r="E95" s="16">
-        <v>12500</v>
+        <v>86</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="13">
+        <v>72000</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="13"/>
       <c r="B96" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C96" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="E96" s="13">
-        <v>14500</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="13"/>
       <c r="B97" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C97" s="13" t="s">
         <v>10</v>
@@ -2342,175 +2393,178 @@
         <v>69</v>
       </c>
       <c r="E97" s="13">
-        <v>18000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="13"/>
       <c r="B98" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C98" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E98" s="13">
-        <v>27000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="13"/>
       <c r="B99" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E99" s="13">
-        <v>14500</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="13"/>
       <c r="B100" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D100" s="13" t="s">
         <v>69</v>
       </c>
       <c r="E100" s="13">
-        <v>14500</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="13"/>
       <c r="B101" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E101" s="13">
-        <v>18000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="13"/>
       <c r="B102" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="E102" s="13">
-        <v>14325</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="13"/>
       <c r="B103" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D103" s="13" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="E103" s="13">
-        <v>8100</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="13"/>
       <c r="B104" t="s">
-        <v>100</v>
-      </c>
-      <c r="C104" s="13"/>
-      <c r="D104" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E104" s="13">
-        <v>8500</v>
+        <v>92</v>
+      </c>
+      <c r="C104" t="s">
+        <v>16</v>
+      </c>
+      <c r="D104" t="s">
+        <v>80</v>
+      </c>
+      <c r="E104" s="16">
+        <v>26000</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="13"/>
       <c r="B105" t="s">
-        <v>100</v>
-      </c>
-      <c r="C105" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E105" s="13">
-        <v>12500</v>
+        <v>92</v>
+      </c>
+      <c r="C105" t="s">
+        <v>20</v>
+      </c>
+      <c r="D105" t="s">
+        <v>80</v>
+      </c>
+      <c r="E105" s="16">
+        <v>24000</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="13"/>
       <c r="B106" t="s">
-        <v>101</v>
-      </c>
-      <c r="C106" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D106" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E106" s="17">
-        <v>25577</v>
+        <v>92</v>
+      </c>
+      <c r="C106" t="s">
+        <v>79</v>
+      </c>
+      <c r="D106" t="s">
+        <v>80</v>
+      </c>
+      <c r="E106" s="16">
+        <v>18000</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="13"/>
       <c r="B107" t="s">
-        <v>102</v>
-      </c>
-      <c r="C107" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D107" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E107" s="17">
-        <v>25577</v>
+        <v>92</v>
+      </c>
+      <c r="C107" t="s">
+        <v>79</v>
+      </c>
+      <c r="D107" t="s">
+        <v>81</v>
+      </c>
+      <c r="E107" s="16">
+        <v>14500</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="13"/>
       <c r="B108" t="s">
-        <v>103</v>
-      </c>
-      <c r="C108" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D108" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E108" s="17">
-        <v>25577</v>
+        <v>92</v>
+      </c>
+      <c r="C108" t="s">
+        <v>79</v>
+      </c>
+      <c r="D108" t="s">
+        <v>82</v>
+      </c>
+      <c r="E108" s="16">
+        <v>12500</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="13"/>
       <c r="B109" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C109" s="13" t="s">
         <v>10</v>
@@ -2523,13 +2577,230 @@
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="13"/>
       <c r="B110" t="s">
+        <v>94</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="13">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="13"/>
+      <c r="B111" t="s">
+        <v>94</v>
+      </c>
+      <c r="C111" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E111" s="13">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="13"/>
+      <c r="B112" t="s">
+        <v>95</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="13">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="13"/>
+      <c r="B113" t="s">
+        <v>96</v>
+      </c>
+      <c r="C113" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D113" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="13">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="13"/>
+      <c r="B114" t="s">
+        <v>97</v>
+      </c>
+      <c r="C114" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D114" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E114" s="13">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="13"/>
+      <c r="B115" t="s">
+        <v>98</v>
+      </c>
+      <c r="C115" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D115" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E115" s="13">
+        <v>14325</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="13"/>
+      <c r="B116" t="s">
+        <v>99</v>
+      </c>
+      <c r="C116" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D116" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E116" s="13">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="13"/>
+      <c r="B117" t="s">
+        <v>100</v>
+      </c>
+      <c r="C117" s="13"/>
+      <c r="D117" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E117" s="13">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="13"/>
+      <c r="B118" t="s">
+        <v>100</v>
+      </c>
+      <c r="C118" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="13">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="13"/>
+      <c r="B119" t="s">
+        <v>101</v>
+      </c>
+      <c r="C119" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E119" s="17">
+        <v>25577</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="13"/>
+      <c r="B120" t="s">
+        <v>102</v>
+      </c>
+      <c r="C120" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D120" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E120" s="17">
+        <v>25577</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="13"/>
+      <c r="B121" t="s">
+        <v>103</v>
+      </c>
+      <c r="C121" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D121" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E121" s="17">
+        <v>25577</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
+        <v>105</v>
+      </c>
+      <c r="C122" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E122" s="13">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
         <v>106</v>
       </c>
-      <c r="D110" s="19" t="s">
+      <c r="D123" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E110" s="20">
+      <c r="E123" s="19">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>107</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E124" s="19">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>108</v>
+      </c>
+      <c r="C125" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D125" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E125" s="19">
         <v>14500</v>
       </c>
     </row>
